--- a/hrdm_training_database.xlsx
+++ b/hrdm_training_database.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,42 +448,62 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Assigned_Duty</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Login_ID</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Password_Hash</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Created_By</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Created_On</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Last_Login</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Failed_Attempts</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Reset_Token</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Reset_Expires</t>
         </is>
       </c>
     </row>
@@ -505,40 +525,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Support/Admin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>admin@classsociety.org</t>
+          <t>System Admin</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>usama.saleem@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>240be518fabd2724ddb6f04eeb1da5967448d7e831c08c8fa822809f74c720a9</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>bc78e58d55cde1346e68f8e5fe588dedf62fa457aa646a500a53347faff6ee24</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Admin@1234</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:49:09</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -560,47 +595,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Support/Admin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>management@classsociety.org</t>
+          <t>Management Oversight</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>management@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>management</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>db2de76b767139bdcdc9ac8468be59cb410c1f1dd882c0af634e762d6c8fe632</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>8e772de1dc75517ec1eeafeab840b4b977dfe92a9f269992fc7eff2e12b72ef8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mgmt@1234</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>USR-TRN-001</t>
+          <t>USR-TRAINER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -615,52 +660,67 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Training Department</t>
+          <t>Support/Admin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>trainer@classsociety.org</t>
+          <t>Training Delivery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>trainer@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>trainer</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>5b3d264e4cdc2c39ca6708b3e1e21f082722be12e63ee21484bdbe15735ab066</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>5150fd76724ee3856394daee240480cd3b363ffaa85cf8507fed91c73bb0ad73</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Trainer@1234</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:16:46</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>USR-SUR-001</t>
+          <t>USR-SURVEYOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Muhammad Ali</t>
+          <t>Sample Surveyor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -670,52 +730,62 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Electrical Survey</t>
+          <t>Survey</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ali@classsociety.org</t>
+          <t>Survey Field Work</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>surveyor@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>surveyor</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ea3d7a717de8ed9429a300d84e17026833c80cb3a9361c5af026a2b7d2e7b4c0</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>896e4acee61a7d206a9dbc961474bb441933a7210096e49123f4be9f162d42ac</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Surveyor@1234</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>USR-APP-001</t>
+          <t>USR-APPRAISER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ahmed Khan</t>
+          <t>Sample Plan Appraiser</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -730,35 +800,700 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ahmed@classsociety.org</t>
+          <t>Plan Appraisal Review</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>appraiser@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>appraiser</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>8c8dbf00186274468f2966c68f335381e618eda5109ee39365deecc40397eff2</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>9b04fab3c992704ccf7205d69e5fe1c303bcdb0c6c3123242f5fefd12f606848</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Appraiser@1234</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USR-QMR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quality Management Rep</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quality Management System</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>QMS Oversight</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>qmr@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>qmr</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6afc291c6ae7d7a851405a1b43d537a189a365088a012a08794a600242983167</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>QMR@1234</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USR-TRAINEE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sample Trainee</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Trainee</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Training Completion</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>trainee@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>trainee</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>331d058620cc2820eea957a8cc8d94ce1ea6c70516ef16c4e3552924e491fc98</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Trainee@1234</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>USR-08932C29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Abdullah Ali</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Surveyor</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Survey</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Survey Team Management</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Abdullah.ali@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>abdullahali</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>621eaa4d8658cf6921145b656b68aa283691d9a002537c738ba2ee2170be97c4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>abdullah@1234</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>USR-D7EE9868</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Usman Zafar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality Management System</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Quality Management, Survey and Audit Reporting</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>usman.zafar@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>usmanzafar</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>9dd0deae474494a67fc759a6bb6f38160daa74f665677ea26c2e47dd067a2383</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>usman@1234</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>USR-C1033DB1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Muhammad Umair</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality Management System</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Quality Management, Survey and Audits</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>m.umair@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>muhammadumair</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>b909a2d32166fc68806ed82b0a85bfd6fb085545e8bc639b5e89e047b0f78b0f</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Mumair@1234</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>USR-4A8678F7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Umair Adeem</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rule Development Rep</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rule Development</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rule Development, Survey and Plan Appraisal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>umair.adeem@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>umairadeem</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>a69163f639f6c7fbebdae3bffc0fd45a60ed9e20b5817fbb4a5cee22dfed7edc</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Umair@1234</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>USR-E6E55B1A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Yahya Hafeez</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Surveyor</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Survey</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Training &amp; Development, Survey and Plan Appraisal</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yahya.hafiz@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>yahyahafeez</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>c9eac80fc41e56b3144e7a79d46695706bd63f3a47e81dd6f5d015af6dfa1776</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>yahya@1234</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>USR-0B6DABD1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Zafar Abbas Babur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Plan Appraisal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Training &amp; Development, Rule Development, Survey and Plan Appraisal</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>zafar.abbas@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>zafarabbasbabur</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>f9a728d89b380dc665e3db61a2db0695fbfda74f7dd1a035baeb1262730fc74b</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Zafar@1234</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Plan Appraisal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Training &amp; Development, Rule Development, Survey and Plan Appraisal</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>usama.saleem@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>usamasaleem</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>cabd0b883a75e8468de121ce499c61f2545ff105e9fc39a6a759aed80e4a336a</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Usama@1234</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:32:40</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USR-115D88E9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Umar Sultan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Surveyor</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Survey</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Survey</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>umar.sultan@psbureau.org</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>umarsultan</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>a24c92ded50c1f17eddfd8390a79672a7cfe1ebfe9140d91134dad4fceb34e48</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Umar@1234</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -773,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,63 +1530,63 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Surveyors</t>
+          <t>Active Users</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plan Appraisers</t>
+          <t>Surveyors</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trainers</t>
+          <t>Plan Appraisers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total Trainings</t>
+          <t>Trainers</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Generated MCQs</t>
+          <t>Total Trainings</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Completed Records</t>
+          <t>Generated MCQs</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -861,7 +1596,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pending Records</t>
+          <t>Completed Records</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -871,42 +1606,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Average Progress %</t>
+          <t>Pending Records</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Certificates Issued</t>
+          <t>Average Progress %</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Activity Logs</t>
+          <t>Certificates Issued</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Activity Logs</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-21 10:07:53</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:34:00</t>
         </is>
       </c>
     </row>
@@ -951,12 +1696,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>APP_VERSION</t>
+          <t>CREATED_ON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026.05.21-secure</t>
+          <t>2026-05-21 21:44:24</t>
         </is>
       </c>
     </row>
@@ -971,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1808,236 @@
       <c r="R1" t="inlineStr">
         <is>
           <t>Last_Updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Basic Survey</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Plan Appraiser, Surveyor, Quality Management Representative, Rule Development Rep, Trainee, On Probation</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>75</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:24:50</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:24:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Basic Survey</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Surveyor, Plan Appraiser, Quality Management Representative, Rule Development Rep, Trainee, On Probation</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>90</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:34:23</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:34:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Basic Survey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Surveyor, Plan Appraiser, Quality Management Representative, Rule Development Rep, Trainee, On Probation</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/presentation/d/18SCy_pTzsXZNqHYzPwNoUX53MBAvcyH7/edit?usp=sharing&amp;ouid=117387528328351609361&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1vJ7WPFIQGofvFa3bucnE4tr_SZKKSMXx/view?usp=sharing</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>80</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Material Added</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:31:43</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TRN-1217DC0E</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Demo 2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Basic Survey</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Surveyor, Plan Appraiser, Quality Management Representative, Rule Development Rep, Trainee, On Probation</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>85</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:50:07</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:50:07</t>
         </is>
       </c>
     </row>
@@ -1194,7 +2169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,6 +2276,1590 @@
       <c r="U1" t="inlineStr">
         <is>
           <t>Last_Updated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REC-A3FAF080</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>USR-QMR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quality Management Rep</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>75</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REC-716A2E04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>USR-08932C29</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Abdullah Ali</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Surveyor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>75</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REC-B81800F3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>USR-D7EE9868</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Usman Zafar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>75</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REC-EAD89A5C</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>USR-C1033DB1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Muhammad Umair</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>75</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REC-D20C8165</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>USR-4A8678F7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Umair Adeem</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rule Development Rep</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>75</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REC-94417621</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>USR-E6E55B1A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yahya Hafeez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Surveyor</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>75</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REC-7BE92FCF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>USR-0B6DABD1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zafar Abbas Babur</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>75</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REC-31E836B4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Activity and functions of IMO and Maritime Administrations</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Recording Viewed</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>75</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>60</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Recording viewed.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REC-5DCA8288</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>USR-QMR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Quality Management Rep</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>90</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REC-85AAF1ED</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>USR-08932C29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Abdullah Ali</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Surveyor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>90</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REC-B3D984BB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>USR-D7EE9868</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Usman Zafar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>90</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REC-CB50A794</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USR-C1033DB1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Muhammad Umair</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quality Management Representative</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>90</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REC-E5B80775</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>USR-4A8678F7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Umair Adeem</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rule Development Rep</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>90</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REC-32D7288C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>USR-E6E55B1A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yahya Hafeez</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Surveyor</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>90</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REC-2806C862</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>USR-0B6DABD1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Zafar Abbas Babur</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>90</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REC-29217E0B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Activity and functions of Classification Societies,</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>90</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>REC-AA2B599C</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Recording Viewed</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>80</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>60</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Recording viewed.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>REC-9494C810</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TRN-1217DC0E</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Demo 2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not Marked</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Not Attempted</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>85</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Not Issued</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Assigned by Admin</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:35</t>
         </is>
       </c>
     </row>
@@ -1457,7 +4016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1515,12 +4074,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LOG-EF9BEC61</t>
+          <t>LOG-CDD09AAB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 10:07:52</t>
+          <t>2026-05-21 21:44:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1543,9 +4102,2947 @@
           <t>Success</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Initial database created.</t>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LOG-DF71E7B5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-21 21:57:47</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LOG-D2C363A4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:00:05</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>User Created</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>USR-08932C29</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LOG-938BFB91</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:01:04</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LOG-03B47AB3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:02:44</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>User Created</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>USR-D7EE9868</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LOG-B5EE49DD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:04:42</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>User Logout</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LOG-2D443890</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:09:13</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LOG-0B32CAEB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:10:43</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>User Created</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>USR-C1033DB1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LOG-D3837997</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:12:26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>User Created</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>USR-4A8678F7</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LOG-2C1F57BF</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:14:40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>User Created</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>USR-E6E55B1A</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LOG-CCF07195</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:16:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>User Created</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>USR-0B6DABD1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LOG-E3771A29</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:17:25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>User Created</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LOG-3B8BC940</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:22:54</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LOG-A0D348B4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:24:50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Training Created</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LOG-C1ED5E8F</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:26:06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>USR-QMR</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LOG-A92F6AE8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:26:06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>USR-08932C29</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LOG-10FC46A8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:26:06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>USR-D7EE9868</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LOG-52822185</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:26:06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>USR-C1033DB1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LOG-DC928B0A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:26:06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>USR-4A8678F7</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOG-717D133D</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:26:06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>USR-E6E55B1A</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LOG-4FE960DD</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:26:07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>USR-0B6DABD1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LOG-0E9C65BF</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:26:07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LOG-EC607FF1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:33:36</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LOG-5532A196</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:34:23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Training Created</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LOG-8A541D9E</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:36:36</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LOG-765A020D</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:21</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>USR-QMR</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LOG-EA66CC9D</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:21</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>USR-08932C29</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LOG-E342674F</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:21</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>USR-D7EE9868</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LOG-A743E664</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:21</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>USR-C1033DB1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LOG-F9191FAC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:22</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>USR-4A8678F7</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LOG-5A7668C7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:22</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>USR-E6E55B1A</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LOG-F04DE265</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:22</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>USR-0B6DABD1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LOG-2DA9371B</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:22</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>TRN-6882A989</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>LOG-0A20AF26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:37:48</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>User Logout</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LOG-C92E2EC2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:38:33</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LOG-E23EC364</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:55:55</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LOG-7A64967F</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:57:46</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>User Logout</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LOG-CEDBACC1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:58:20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LOG-F3CF71B8</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:58:47</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Slides Opened</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Slides completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LOG-ED691CC2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-21 22:59:58</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Recording Viewed</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LOG-1ACDC04E</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-21 23:00:01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Video Opened</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Video completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LOG-E505CC11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-21 23:00:07</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Video Opened</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Video completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LOG-739BB0F2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-21 23:00:11</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Recording Viewed</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TRN-C7A35F82</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LOG-415CCEE7</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:29:14</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LOG-54E04F93</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:30:40</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>User Created</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>USR-115D88E9</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LOG-1E0C01AD</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:31:43</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Training Created</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LOG-DEF37966</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:49:09</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LOG-90D98AAA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:49:42</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LOG-7FAFB235</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:50:07</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Training Created</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TRN-1217DC0E</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LOG-88993CFF</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:50:20</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Training Assigned</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TRN-1217DC0E</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>LOG-CF082F1F</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:50:39</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>User Logout</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Admin User</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>USR-ADMIN</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LOG-8A5F1993</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-05-22 06:53:21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LOG-5B678B06</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:06:18</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>LOG-00E2B3CB</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:06:19</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Training Links Saved</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>LOG-AF7E21C7</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:06:33</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Training Links Saved</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LOG-E9E25307</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:16:46</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>LOG-C8B417E1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:32:08</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>User Logout</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LOG-D8CD1800</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:32:41</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LOG-AD384E0C</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Slides Opened</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Slides completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LOG-5ABA6998</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:14</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Slides Opened</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Slides completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LOG-58F53C9A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Video Opened</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Video completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LOG-CD51D804</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Video Opened</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Video completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LOG-A29ED641</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Recording Viewed</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LOG-08DDDDCB</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:34</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Recording Viewed</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LOG-32D4CC22</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05-22 07:33:59</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>User Logout</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Success</t>
         </is>
       </c>
     </row>

--- a/hrdm_training_database.xlsx
+++ b/hrdm_training_database.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-05-22 07:16:46</t>
+          <t>2026-05-22 14:33:17</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-05-22 07:32:40</t>
+          <t>2026-05-22 14:36:21</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 07:34:00</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,32 @@
           <t>https://drive.google.com/file/d/1vJ7WPFIQGofvFa3bucnE4tr_SZKKSMXx/view?usp=sharing</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/l/meeting/new?subject=Demo+-+TRN-27045916&amp;content=Training+ID%3A+TRN-27045916%0ATraining+Title%3A+Demo%0ASchedule%3A+2026-05-22+10%3A00+AM%0A%0APlease+join+this+HRDM+training+session+through+Microsoft+Teams.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://jb,jnj</t>
+        </is>
+      </c>
       <c r="N4" t="n">
         <v>80</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Material Added</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1982,7 +2002,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-22 07:06:33</t>
+          <t>2026-05-22 14:35:13</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2109,895 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>Uploaded_On</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CONTENT-0E3E647E</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>kk.txt</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING
+Subject: Technical and Financial Justification for Installation of 6 kW Hybrid Solar System with Lithium-Ion Battery Storage
+It is submitted for kind consideration that the proposed 6 kW Hybrid Solar System equipped with Hybrid Inverter and Lithium-Ion Battery Storage is technically and financially evaluated.
+1.	Price Rationalization &amp; Negotiation Aspect
+It is submitted that detailed financial working and market comparison carried out through the attached comparative analysis reflects that the estimated average market value of the required solar systems is approximately Rs. 2,753,445/-.
+However, the quoted price submitted by M/s Solar Square for the proposed installation is Rs. 3,637,851/-, which is considerably higher than the calculated average market assessment.
+In view of the above, it is considered appropriate that the quoted rates may further be negotiated with the firm in order to achieve a more economical and competitive price while maintaining the required technical specifications, quality standards, warranty coverage, and system performance.
+Since the procurement involves multiple hybrid systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization. Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum financial benefit to the organization.
+2.	System Energy Production &amp; Financial Analysis
+The proposed solar system is designed on the basis that each installed kilowatt (kW) of solar capacity produces approximately 4 units (kWh) of electricity per day under normal operating conditions. Accordingly:
+o	Installed Capacity = 6 kW
+o	Daily Generation per kW = 4 Units
+o	Total Daily Generation = 24 Units per Day
+Considering 5 effective working sunlight days per week:
+o	Weekly Generation = 24 × 5 = 120 Units
+o	Monthly Generation = 120 × 4.33 = approximately 520 Units per Month
+The current electricity tariff is approximately Rs. 50 per unit, therefore:
+o	Estimated Monthly Savings = 520 × 50
+o	Estimated Monthly Savings = Rs. 26,000/- per month
+The approximate cost of a complete 6 kW Hybrid Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs. 1,000,000/- (10 lacs).
+Hence:
+o	Estimated Payback Period = 1,000,000 ÷ 26,000
+o	Approximate Payback Period = 3.2 years
+After completion of the payback period, the generated electricity shall effectively become a long-term financial saving for the organization/user.
+3.	Limitations of Conventional Desi Inverter Systems
+It is further observed that conventional/desi inverter solar systems are not technically adequate for efficient energy management due to the following reasons:
+o	Peak solar production is not fully utilized effectively.
+o	Conventional liquid batteries generally provide only around 50% usable capacity of their rated storage.
+o	The effective service life of liquid batteries is usually limited to 1–2 years maximum, resulting in frequent replacement costs.
+o	System efficiency and reliability remain comparatively low.
+o	Maintenance requirements and operational losses are significantly higher.
+4.	Benefits of Hybrid Solar System with Lithium-Ion Battery
+In view of the revised net metering policies, the financial benefits of exporting excess power to the grid have reduced considerably. Therefore, installation of a Hybrid Solar System integrated with a state-of-the-art Lithium-Ion Battery and Hybrid Inverter is considered more beneficial due to the following advantages:
+o	Maximum utilization of solar generation during peak hours.
+o	High-efficiency energy storage and backup capability.
+o	Lithium-Ion batteries provide significantly longer service life compared to liquid batteries.
+o	Higher depth of discharge and better energy utilization.
+o	Reduced maintenance and replacement costs.
+o	Improved system reliability, operational stability, and uninterrupted power availability.
+o	Better return on investment under current net metering regulations.
+In view of the above technical and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CONTENT-CBA6FE9C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING BFC Satellite Town.docx</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CONTENT-E8EEB800</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IEEE_Conference_Defense_Final_Visual.pptx</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CONTENT-0B3F4D78</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Solis_Warranty-International-20250701-5years.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CONTENT-BC15FE16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING BFC Satellite Town.docx</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CONTENT-49442CED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IEEE_Conference_Defense_Final_Visual.pptx</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CONTENT-0DAAE8FB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Solis_Warranty-International-20250701-5years.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CONTENT-4109A26D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>kk.txt</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING
+Subject: Technical and Financial Justification for Installation of 6 kW Hybrid Solar System with Lithium-Ion Battery Storage
+It is submitted for kind consideration that the proposed 6 kW Hybrid Solar System equipped with Hybrid Inverter and Lithium-Ion Battery Storage is technically and financially evaluated.
+1.	Price Rationalization &amp; Negotiation Aspect
+It is submitted that detailed financial working and market comparison carried out through the attached comparative analysis reflects that the estimated average market value of the required solar systems is approximately Rs. 2,753,445/-.
+However, the quoted price submitted by M/s Solar Square for the proposed installation is Rs. 3,637,851/-, which is considerably higher than the calculated average market assessment.
+In view of the above, it is considered appropriate that the quoted rates may further be negotiated with the firm in order to achieve a more economical and competitive price while maintaining the required technical specifications, quality standards, warranty coverage, and system performance.
+Since the procurement involves multiple hybrid systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization. Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum financial benefit to the organization.
+2.	System Energy Production &amp; Financial Analysis
+The proposed solar system is designed on the basis that each installed kilowatt (kW) of solar capacity produces approximately 4 units (kWh) of electricity per day under normal operating conditions. Accordingly:
+o	Installed Capacity = 6 kW
+o	Daily Generation per kW = 4 Units
+o	Total Daily Generation = 24 Units per Day
+Considering 5 effective working sunlight days per week:
+o	Weekly Generation = 24 × 5 = 120 Units
+o	Monthly Generation = 120 × 4.33 = approximately 520 Units per Month
+The current electricity tariff is approximately Rs. 50 per unit, therefore:
+o	Estimated Monthly Savings = 520 × 50
+o	Estimated Monthly Savings = Rs. 26,000/- per month
+The approximate cost of a complete 6 kW Hybrid Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs. 1,000,000/- (10 lacs).
+Hence:
+o	Estimated Payback Period = 1,000,000 ÷ 26,000
+o	Approximate Payback Period = 3.2 years
+After completion of the payback period, the generated electricity shall effectively become a long-term financial saving for the organization/user.
+3.	Limitations of Conventional Desi Inverter Systems
+It is further observed that conventional/desi inverter solar systems are not technically adequate for efficient energy management due to the following reasons:
+o	Peak solar production is not fully utilized effectively.
+o	Conventional liquid batteries generally provide only around 50% usable capacity of their rated storage.
+o	The effective service life of liquid batteries is usually limited to 1–2 years maximum, resulting in frequent replacement costs.
+o	System efficiency and reliability remain comparatively low.
+o	Maintenance requirements and operational losses are significantly higher.
+4.	Benefits of Hybrid Solar System with Lithium-Ion Battery
+In view of the revised net metering policies, the financial benefits of exporting excess power to the grid have reduced considerably. Therefore, installation of a Hybrid Solar System integrated with a state-of-the-art Lithium-Ion Battery and Hybrid Inverter is considered more beneficial due to the following advantages:
+o	Maximum utilization of solar generation during peak hours.
+o	High-efficiency energy storage and backup capability.
+o	Lithium-Ion batteries provide significantly longer service life compared to liquid batteries.
+o	Higher depth of discharge and better energy utilization.
+o	Reduced maintenance and replacement costs.
+o	Improved system reliability, operational stability, and uninterrupted power availability.
+o	Better return on investment under current net metering regulations.
+In view of the above technical and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONTENT-506E142F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING BFC Satellite Town.docx</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING
+Subject: Technical and Financial Justification for Installation of 6 kW Hybrid Solar System with Lithium-Ion Battery Storage
+It is submitted for kind consideration that the proposed 6 kW Hybrid Solar System equipped with Hybrid Inverter and Lithium-Ion Battery Storage is technically and financially evaluated.
+Price Rationalization &amp; Negotiation Aspect
+It is submitted that detailed financial working and market comparison carried out through the attached comparative analysis reflects that the estimated average market value of the required solar systems is approximately Rs. 2,753,445/-.
+However, the quoted price submitted by M/s Solar Square for the proposed installation is Rs. 3,637,851/-, which is considerably higher than the calculated average market assessment.
+In view of the above, it is considered appropriate that the quoted rates may further be negotiated with the firm in order to achieve a more economical and competitive price while maintaining the required technical specifications, quality standards, warranty coverage, and system performance.
+Since the procurement involves multiple hybrid systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization. Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum financial benefit to the organization.
+System Energy Production &amp; Financial Analysis
+The proposed solar system is designed on the basis that each installed kilowatt (kW) of solar capacity produces approximately 4 units (kWh) of electricity per day under normal operating conditions. Accordingly:
+Installed Capacity = 6 kW
+Daily Generation per kW = 4 Units
+Total Daily Generation = 24 Units per Day
+Considering 5 effective working sunlight days per week:
+Weekly Generation = 24 × 5 = 120 Units
+Monthly Generation = 120 × 4.33 = approximately 520 Units per Month
+The current electricity tariff is approximately Rs. 50 per unit, therefore:
+Estimated Monthly Savings = 520 × 50
+Estimated Monthly Savings = Rs. 26,000/- per month
+The approximate cost of a complete 6 kW Hybrid Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs. 1,000,000/- (10 lacs).
+Hence:
+Estimated Payback Period = 1,000,000 ÷ 26,000
+Approximate Payback Period = 3.2 years
+After completion of the payback period, the generated electricity shall effectively become a long-term financial saving for the organization/user.
+Limitations of Conventional Desi Inverter Systems
+It is further observed that conventional/desi inverter solar systems are not technically adequate for efficient energy management due to the following reasons:
+Peak solar production is not fully utilized effectively.
+Conventional liquid batteries generally provide only around 50% usable capacity of their rated storage.
+The effective service life of liquid batteries is usually limited to 1–2 years maximum, resulting in frequent replacement costs.
+System efficiency and reliability remain comparatively low.
+Maintenance requirements and operational losses are significantly higher.
+Benefits of Hybrid Solar System with Lithium-Ion Battery
+In view of the revised net metering policies, the financial benefits of exporting excess power to the grid have reduced considerably. Therefore, installation of a Hybrid Solar System integrated with a state-of-the-art Lithium-Ion Battery and Hybrid Inverter is considered more beneficial due to the following advantages:
+Maximum utilization of solar generation during peak hours.
+High-efficiency energy storage and backup capability.
+Lithium-Ion batteries provide significantly longer service life compared to liquid batteries.
+Higher depth of discharge and better energy utilization.
+Reduced maintenance and replacement costs.
+Improved system reliability, operational stability, and uninterrupted power availability.
+Better return on investment under current net metering regulations.
+In view of the above technical and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CONTENT-55081073</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING BFC Satellite Town.docx</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING
+Subject: Technical and Financial Justification for Installation of 6 kW Hybrid Solar System with Lithium-Ion Battery Storage
+It is submitted for kind consideration that the proposed 6 kW Hybrid Solar System equipped with Hybrid Inverter and Lithium-Ion Battery Storage is technically and financially evaluated.
+Price Rationalization &amp; Negotiation Aspect
+It is submitted that detailed financial working and market comparison carried out through the attached comparative analysis reflects that the estimated average market value of the required solar systems is approximately Rs. 2,753,445/-.
+However, the quoted price submitted by M/s Solar Square for the proposed installation is Rs. 3,637,851/-, which is considerably higher than the calculated average market assessment.
+In view of the above, it is considered appropriate that the quoted rates may further be negotiated with the firm in order to achieve a more economical and competitive price while maintaining the required technical specifications, quality standards, warranty coverage, and system performance.
+Since the procurement involves multiple hybrid systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization. Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum financial benefit to the organization.
+System Energy Production &amp; Financial Analysis
+The proposed solar system is designed on the basis that each installed kilowatt (kW) of solar capacity produces approximately 4 units (kWh) of electricity per day under normal operating conditions. Accordingly:
+Installed Capacity = 6 kW
+Daily Generation per kW = 4 Units
+Total Daily Generation = 24 Units per Day
+Considering 5 effective working sunlight days per week:
+Weekly Generation = 24 × 5 = 120 Units
+Monthly Generation = 120 × 4.33 = approximately 520 Units per Month
+The current electricity tariff is approximately Rs. 50 per unit, therefore:
+Estimated Monthly Savings = 520 × 50
+Estimated Monthly Savings = Rs. 26,000/- per month
+The approximate cost of a complete 6 kW Hybrid Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs. 1,000,000/- (10 lacs).
+Hence:
+Estimated Payback Period = 1,000,000 ÷ 26,000
+Approximate Payback Period = 3.2 years
+After completion of the payback period, the generated electricity shall effectively become a long-term financial saving for the organization/user.
+Limitations of Conventional Desi Inverter Systems
+It is further observed that conventional/desi inverter solar systems are not technically adequate for efficient energy management due to the following reasons:
+Peak solar production is not fully utilized effectively.
+Conventional liquid batteries generally provide only around 50% usable capacity of their rated storage.
+The effective service life of liquid batteries is usually limited to 1–2 years maximum, resulting in frequent replacement costs.
+System efficiency and reliability remain comparatively low.
+Maintenance requirements and operational losses are significantly higher.
+Benefits of Hybrid Solar System with Lithium-Ion Battery
+In view of the revised net metering policies, the financial benefits of exporting excess power to the grid have reduced considerably. Therefore, installation of a Hybrid Solar System integrated with a state-of-the-art Lithium-Ion Battery and Hybrid Inverter is considered more beneficial due to the following advantages:
+Maximum utilization of solar generation during peak hours.
+High-efficiency energy storage and backup capability.
+Lithium-Ion batteries provide significantly longer service life compared to liquid batteries.
+Higher depth of discharge and better energy utilization.
+Reduced maintenance and replacement costs.
+Improved system reliability, operational stability, and uninterrupted power availability.
+Better return on investment under current net metering regulations.
+In view of the above technical and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CONTENT-C0092A97</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Liquid_Cooling_Dissertation_Presentation.pptx</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONTENT-7933E50E</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING BFC Satellite Town.docx</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING
+Subject: Technical and Financial Justification for Installation of 6 kW Hybrid Solar System with Lithium-Ion Battery Storage
+It is submitted for kind consideration that the proposed 6 kW Hybrid Solar System equipped with Hybrid Inverter and Lithium-Ion Battery Storage is technically and financially evaluated.
+Price Rationalization &amp; Negotiation Aspect
+It is submitted that detailed financial working and market comparison carried out through the attached comparative analysis reflects that the estimated average market value of the required solar systems is approximately Rs. 2,753,445/-.
+However, the quoted price submitted by M/s Solar Square for the proposed installation is Rs. 3,637,851/-, which is considerably higher than the calculated average market assessment.
+In view of the above, it is considered appropriate that the quoted rates may further be negotiated with the firm in order to achieve a more economical and competitive price while maintaining the required technical specifications, quality standards, warranty coverage, and system performance.
+Since the procurement involves multiple hybrid systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization. Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum financial benefit to the organization.
+System Energy Production &amp; Financial Analysis
+The proposed solar system is designed on the basis that each installed kilowatt (kW) of solar capacity produces approximately 4 units (kWh) of electricity per day under normal operating conditions. Accordingly:
+Installed Capacity = 6 kW
+Daily Generation per kW = 4 Units
+Total Daily Generation = 24 Units per Day
+Considering 5 effective working sunlight days per week:
+Weekly Generation = 24 × 5 = 120 Units
+Monthly Generation = 120 × 4.33 = approximately 520 Units per Month
+The current electricity tariff is approximately Rs. 50 per unit, therefore:
+Estimated Monthly Savings = 520 × 50
+Estimated Monthly Savings = Rs. 26,000/- per month
+The approximate cost of a complete 6 kW Hybrid Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs. 1,000,000/- (10 lacs).
+Hence:
+Estimated Payback Period = 1,000,000 ÷ 26,000
+Approximate Payback Period = 3.2 years
+After completion of the payback period, the generated electricity shall effectively become a long-term financial saving for the organization/user.
+Limitations of Conventional Desi Inverter Systems
+It is further observed that conventional/desi inverter solar systems are not technically adequate for efficient energy management due to the following reasons:
+Peak solar production is not fully utilized effectively.
+Conventional liquid batteries generally provide only around 50% usable capacity of their rated storage.
+The effective service life of liquid batteries is usually limited to 1–2 years maximum, resulting in frequent replacement costs.
+System efficiency and reliability remain comparatively low.
+Maintenance requirements and operational losses are significantly higher.
+Benefits of Hybrid Solar System with Lithium-Ion Battery
+In view of the revised net metering policies, the financial benefits of exporting excess power to the grid have reduced considerably. Therefore, installation of a Hybrid Solar System integrated with a state-of-the-art Lithium-Ion Battery and Hybrid Inverter is considered more beneficial due to the following advantages:
+Maximum utilization of solar generation during peak hours.
+High-efficiency energy storage and backup capability.
+Lithium-Ion batteries provide significantly longer service life compared to liquid batteries.
+Higher depth of discharge and better energy utilization.
+Reduced maintenance and replacement costs.
+Improved system reliability, operational stability, and uninterrupted power availability.
+Better return on investment under current net metering regulations.
+In view of the above technical and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CONTENT-F019300D</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Liquid_Cooling_Dissertation_Presentation.pptx</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONTENT-8F4141E0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING BFC Satellite Town.docx</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING
+Subject: Technical and Financial Justification for Installation of 6 kW Hybrid Solar System with Lithium-Ion Battery Storage
+It is submitted for kind consideration that the proposed 6 kW Hybrid Solar System equipped with Hybrid Inverter and Lithium-Ion Battery Storage is technically and financially evaluated.
+Price Rationalization &amp; Negotiation Aspect
+It is submitted that detailed financial working and market comparison carried out through the attached comparative analysis reflects that the estimated average market value of the required solar systems is approximately Rs. 2,753,445/-.
+However, the quoted price submitted by M/s Solar Square for the proposed installation is Rs. 3,637,851/-, which is considerably higher than the calculated average market assessment.
+In view of the above, it is considered appropriate that the quoted rates may further be negotiated with the firm in order to achieve a more economical and competitive price while maintaining the required technical specifications, quality standards, warranty coverage, and system performance.
+Since the procurement involves multiple hybrid systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization. Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum financial benefit to the organization.
+System Energy Production &amp; Financial Analysis
+The proposed solar system is designed on the basis that each installed kilowatt (kW) of solar capacity produces approximately 4 units (kWh) of electricity per day under normal operating conditions. Accordingly:
+Installed Capacity = 6 kW
+Daily Generation per kW = 4 Units
+Total Daily Generation = 24 Units per Day
+Considering 5 effective working sunlight days per week:
+Weekly Generation = 24 × 5 = 120 Units
+Monthly Generation = 120 × 4.33 = approximately 520 Units per Month
+The current electricity tariff is approximately Rs. 50 per unit, therefore:
+Estimated Monthly Savings = 520 × 50
+Estimated Monthly Savings = Rs. 26,000/- per month
+The approximate cost of a complete 6 kW Hybrid Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs. 1,000,000/- (10 lacs).
+Hence:
+Estimated Payback Period = 1,000,000 ÷ 26,000
+Approximate Payback Period = 3.2 years
+After completion of the payback period, the generated electricity shall effectively become a long-term financial saving for the organization/user.
+Limitations of Conventional Desi Inverter Systems
+It is further observed that conventional/desi inverter solar systems are not technically adequate for efficient energy management due to the following reasons:
+Peak solar production is not fully utilized effectively.
+Conventional liquid batteries generally provide only around 50% usable capacity of their rated storage.
+The effective service life of liquid batteries is usually limited to 1–2 years maximum, resulting in frequent replacement costs.
+System efficiency and reliability remain comparatively low.
+Maintenance requirements and operational losses are significantly higher.
+Benefits of Hybrid Solar System with Lithium-Ion Battery
+In view of the revised net metering policies, the financial benefits of exporting excess power to the grid have reduced considerably. Therefore, installation of a Hybrid Solar System integrated with a state-of-the-art Lithium-Ion Battery and Hybrid Inverter is considered more beneficial due to the following advantages:
+Maximum utilization of solar generation during peak hours.
+High-efficiency energy storage and backup capability.
+Lithium-Ion batteries provide significantly longer service life compared to liquid batteries.
+Higher depth of discharge and better energy utilization.
+Reduced maintenance and replacement costs.
+Improved system reliability, operational stability, and uninterrupted power availability.
+Better return on investment under current net metering regulations.
+In view of the above technical and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CONTENT-4E2F8C23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Liquid_Cooling_Dissertation_Presentation.pptx</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CONTENT-A077B15E</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Liquid_Cooling_Dissertation_Presentation.pptx</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONTENT-DF97BD30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Babur saleem (2).pdf</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Babur
+Saleem
+RAJ
+A
+Honorary
+Sub
+Lieutenant
+(
+S
+D
+)
+M
+S
+(
+Retd
+)
+PN
+PROFILE  
+Accomplished healthcare and administrative professional with 34 years of 
+distinguished service in the Pakistan Navy’s Medical Branch. Specialized in medical 
+services, operational administration, and preventive healthcare across leading naval 
+hospitals and bases including PNS Shifa , PNS Rahat, PNS  Darmaan Jah , PNS Shifa /NCS, 
+PNS Bahadur, PNS Karsaz, PN S Dilawar , Patron 10 Squadron , Headquarter  PMSA  and 
+PNS Abdoze / Submarine Squadron. Proven record in training, supervision, ward 
+management, and departmental administration under high -pressure environments. 
+Recognized for leadership, operational excellence, and dedication to patient car e and 
+organizational efficiency.  
+EDUCATION  
+Matriculation – Science (1989)  
+Rawalpindi Board  
+CONTACT
+ PHONE :
+ +92-346-2657026
+ EMAIL :
+ babarsaleem 7866 @gmail .com
+REFERENCE
+ Commandant
+ PNS
+ Shifa
+ +021 -48506503
+ Commandant
+ PNS
+ Rahat
+ +021 -48503608
+WORK EXPERIENCE  
+PNS SHIFA PNS RAHAT PNS KARSAZ PNS BAHADUR PNS DILAWAR PNS QASIM  
+• Medical Technician                  General Nursing Technician  
+• Ward Administration              Departmental Administrat ion  
+PATRON 10 SQUADRON  
+• Petty Office Incharge Sickbay  
+Naval Center Surgery (NCS)  
+• Personal  Secretary  to Staff  Surgeon  
+• Chief Admin         Chief Security                Chief Maintenance  
+Naval Officer Residential Estate Sickbay  
+• Chief Petty officer Incharge MI ROOM  
+HEAQUARTER PMSA  
+• Petty Office Incharge Sickbay  
+PNS ABDOZE / SUBMARINE SQUADRON   
+• Chief  Petty officer  Incharge Sickbay  
+PNS Darmaan Jah Hospital  
+• Chief Admin  
+PROFESSIONAL COURSES  
+•                              
+ 		General  Nursing  Technician
+              •
+ Chief  Medical  Artificer
+                         •
+ Security  &amp; Weapon  Training
+              •
+ S&amp;W Training  for MCPO
+SKILLS
+ 100%100%90%100%100%100%90%
+First Aid &amp; Casualty ManagementMaintenanceSecurity &amp; WeaponDepartmental AdmininstrationWards AdministrationMedical Eqipment HandlingLecture &amp; Teaching• Junior Leader Course  
+• Sea Survival  
+• HRM  Course  
+• Leading  Medical  Technician  
+• Medical  Technician</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONTENT-07F1D5F3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING BFC Satellite Town.docx</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING
+Subject: Technical and Financial Justification for Installation of 6 kW Hybrid Solar System with Lithium-Ion Battery Storage
+It is submitted for kind consideration that the proposed 6 kW Hybrid Solar System equipped with Hybrid Inverter and Lithium-Ion Battery Storage is technically and financially evaluated.
+Price Rationalization &amp; Negotiation Aspect
+It is submitted that detailed financial working and market comparison carried out through the attached comparative analysis reflects that the estimated average market value of the required solar systems is approximately Rs. 2,753,445/-.
+However, the quoted price submitted by M/s Solar Square for the proposed installation is Rs. 3,637,851/-, which is considerably higher than the calculated average market assessment.
+In view of the above, it is considered appropriate that the quoted rates may further be negotiated with the firm in order to achieve a more economical and competitive price while maintaining the required technical specifications, quality standards, warranty coverage, and system performance.
+Since the procurement involves multiple hybrid systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization. Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum financial benefit to the organization.
+System Energy Production &amp; Financial Analysis
+The proposed solar system is designed on the basis that each installed kilowatt (kW) of solar capacity produces approximately 4 units (kWh) of electricity per day under normal operating conditions. Accordingly:
+Installed Capacity = 6 kW
+Daily Generation per kW = 4 Units
+Total Daily Generation = 24 Units per Day
+Considering 5 effective working sunlight days per week:
+Weekly Generation = 24 × 5 = 120 Units
+Monthly Generation = 120 × 4.33 = approximately 520 Units per Month
+The current electricity tariff is approximately Rs. 50 per unit, therefore:
+Estimated Monthly Savings = 520 × 50
+Estimated Monthly Savings = Rs. 26,000/- per month
+The approximate cost of a complete 6 kW Hybrid Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs. 1,000,000/- (10 lacs).
+Hence:
+Estimated Payback Period = 1,000,000 ÷ 26,000
+Approximate Payback Period = 3.2 years
+After completion of the payback period, the generated electricity shall effectively become a long-term financial saving for the organization/user.
+Limitations of Conventional Desi Inverter Systems
+It is further observed that conventional/desi inverter solar systems are not technically adequate for efficient energy management due to the following reasons:
+Peak solar production is not fully utilized effectively.
+Conventional liquid batteries generally provide only around 50% usable capacity of their rated storage.
+The effective service life of liquid batteries is usually limited to 1–2 years maximum, resulting in frequent replacement costs.
+System efficiency and reliability remain comparatively low.
+Maintenance requirements and operational losses are significantly higher.
+Benefits of Hybrid Solar System with Lithium-Ion Battery
+In view of the revised net metering policies, the financial benefits of exporting excess power to the grid have reduced considerably. Therefore, installation of a Hybrid Solar System integrated with a state-of-the-art Lithium-Ion Battery and Hybrid Inverter is considered more beneficial due to the following advantages:
+Maximum utilization of solar generation during peak hours.
+High-efficiency energy storage and backup capability.
+Lithium-Ion batteries provide significantly longer service life compared to liquid batteries.
+Higher depth of discharge and better energy utilization.
+Reduced maintenance and replacement costs.
+Improved system reliability, operational stability, and uninterrupted power availability.
+Better return on investment under current net metering regulations.
+In view of the above technical and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONTENT-AABF5739</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING BFC Satellite Town.docx</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>docx</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MINUTE NOTING
+Subject: Technical and Financial Justification for Installation of 6 kW Hybrid Solar System with Lithium-Ion Battery Storage
+It is submitted for kind consideration that the proposed 6 kW Hybrid Solar System equipped with Hybrid Inverter and Lithium-Ion Battery Storage is technically and financially evaluated.
+Price Rationalization &amp; Negotiation Aspect
+It is submitted that detailed financial working and market comparison carried out through the attached comparative analysis reflects that the estimated average market value of the required solar systems is approximately Rs. 2,753,445/-.
+However, the quoted price submitted by M/s Solar Square for the proposed installation is Rs. 3,637,851/-, which is considerably higher than the calculated average market assessment.
+In view of the above, it is considered appropriate that the quoted rates may further be negotiated with the firm in order to achieve a more economical and competitive price while maintaining the required technical specifications, quality standards, warranty coverage, and system performance.
+Since the procurement involves multiple hybrid systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization. Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum financial benefit to the organization.
+System Energy Production &amp; Financial Analysis
+The proposed solar system is designed on the basis that each installed kilowatt (kW) of solar capacity produces approximately 4 units (kWh) of electricity per day under normal operating conditions. Accordingly:
+Installed Capacity = 6 kW
+Daily Generation per kW = 4 Units
+Total Daily Generation = 24 Units per Day
+Considering 5 effective working sunlight days per week:
+Weekly Generation = 24 × 5 = 120 Units
+Monthly Generation = 120 × 4.33 = approximately 520 Units per Month
+The current electricity tariff is approximately Rs. 50 per unit, therefore:
+Estimated Monthly Savings = 520 × 50
+Estimated Monthly Savings = Rs. 26,000/- per month
+The approximate cost of a complete 6 kW Hybrid Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs. 1,000,000/- (10 lacs).
+Hence:
+Estimated Payback Period = 1,000,000 ÷ 26,000
+Approximate Payback Period = 3.2 years
+After completion of the payback period, the generated electricity shall effectively become a long-term financial saving for the organization/user.
+Limitations of Conventional Desi Inverter Systems
+It is further observed that conventional/desi inverter solar systems are not technically adequate for efficient energy management due to the following reasons:
+Peak solar production is not fully utilized effectively.
+Conventional liquid batteries generally provide only around 50% usable capacity of their rated storage.
+The effective service life of liquid batteries is usually limited to 1–2 years maximum, resulting in frequent replacement costs.
+System efficiency and reliability remain comparatively low.
+Maintenance requirements and operational losses are significantly higher.
+Benefits of Hybrid Solar System with Lithium-Ion Battery
+In view of the revised net metering policies, the financial benefits of exporting excess power to the grid have reduced considerably. Therefore, installation of a Hybrid Solar System integrated with a state-of-the-art Lithium-Ion Battery and Hybrid Inverter is considered more beneficial due to the following advantages:
+Maximum utilization of solar generation during peak hours.
+High-efficiency energy storage and backup capability.
+Lithium-Ion batteries provide significantly longer service life compared to liquid batteries.
+Higher depth of discharge and better energy utilization.
+Reduced maintenance and replacement costs.
+Improved system reliability, operational stability, and uninterrupted power availability.
+Better return on investment under current net metering regulations.
+In view of the above technical and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
         </is>
       </c>
     </row>
@@ -2103,7 +3012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2155,6 +3064,3114 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>Generated_On</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q-8CF07DA2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>50 per unit, therefore:
+ o	__________ Monthly Savings = 520 × 50
+ o	Estimated Monthly Savings = Rs.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Reflects</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Maintaining</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q-02D23613</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>o	__________ depth of discharge and better energy utilization.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q-08605D0C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>26,000/- per month
+ The approximate cost of a complete 6 kW __________ Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Evaluated</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q-F161D674</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum __________ benefit to the organization.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Quoted</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Therefore</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Q-A244BA7D</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>o	__________ batteries provide significantly longer service life compared to liquid batteries.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Aspect</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Q-E3EAFB78</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>However, the quoted price submitted by M/s Solar Square for the proposed __________ is Rs.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Evaluated</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Q-6AECD315</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3,637,851/-, which is considerably higher than the calculated average __________ assessment.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Negotiated</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Equipped</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Negotiation</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Q-F9A964EE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>o	Conventional liquid batteries generally provide only around 50% usable capacity of their rated __________.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kindly</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Q-26D02954</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>o	High-efficiency energy __________ and backup capability.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Negotiated</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Considerably</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Q-C552BC33</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>o	Maintenance requirements and operational losses are significantly __________.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Financially</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Maintaining</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Approximately</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q-F9059A3F</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Benefits of Hybrid Solar System with Lithium-Ion Battery
+ In view of the revised net metering policies, the __________ benefits of exporting excess power to the grid have reduced considerably.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Since</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Accorded</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Q-0B1BA9A9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>In view of the above __________ and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Negotiation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Since</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Q-8887EAE1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Since the procurement involves multiple __________ systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Considerably</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Q-D5034EF9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>In view of the above __________ and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Accorded</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Q-7797BBF1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3,637,851/-, which is considerably higher than the calculated average __________ assessment.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Involves</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Maintaining</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q-27E1CC4D</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Benefits of Hybrid Solar System with Lithium-Ion Battery
+ In view of the revised net metering policies, the __________ benefits of exporting excess power to the grid have reduced considerably.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Square</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>However</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-CE8405C4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>26,000/- per month
+ The approximate cost of a complete 6 kW __________ Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Considerably</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>However</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rates</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q-5129E665</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>o	High-efficiency energy __________ and backup capability.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Approximately</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q-4B6A60D4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>o	Conventional liquid batteries generally provide only around 50% usable capacity of their rated __________.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Involves</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Reasonable</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q-63F7D40C</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>o	__________ depth of discharge and better energy utilization.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q-4BAAFDC0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Since the procurement involves multiple __________ systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Approximately</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Noting</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q-BA7BB5E3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>o	__________ batteries provide significantly longer service life compared to liquid batteries.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Warranty</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rationalization</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q-E2BE21F2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>o	Maintenance requirements and operational losses are significantly __________.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Aspect</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Square</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q-68F2E6F0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>50 per unit, therefore:
+ o	__________ Monthly Savings = 520 × 50
+ o	Estimated Monthly Savings = Rs.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Maintaining</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q-DF7F0BDF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>However, the quoted price submitted by M/s Solar Square for the proposed __________ is Rs.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Rationalization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Considered</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q-BDA77563</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum __________ benefit to the organization.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q-22A1BF22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Since the procurement involves multiple __________ systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>However</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Noting</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q-D18B6D63</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>__________ depth of discharge and better energy utilization.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rates</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Satellite</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q-2B64698E</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>However, the quoted price submitted by M/s Solar Square for the proposed __________ is Rs.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Maintaining</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q-E3BC3054</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>In view of the above __________ and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Attached</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Comparative</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q-249D2D97</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Benefits of Hybrid Solar System with Lithium-Ion Battery In view of the revised net metering policies, the __________ benefits of exporting excess power to the grid have reduced considerably.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Considerably</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Equipped</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q-6F56A6DE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hence: Estimated Payback Period = 1,000,000 ÷ 26,000 Approximate Payback Period = 3.2 years After completion of the payback period, the generated electricity shall effectively become a long-term __________ saving for the organization/user.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Since</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Equipped</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q-3EF50EA2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>High-efficiency energy __________ and backup capability.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Standards</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Accorded</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carried</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q-FF70F067</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Conventional liquid batteries generally provide only around 50% usable capacity of their rated __________.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q-BB979D32</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum __________ benefit to the organization.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Therefore</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q-8092B46B</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Maintenance requirements and operational losses are significantly __________.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Comparative</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Technically</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q-088FC88B</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Recognized for leadership, __________ excellence, and dedication to patient car e and  organizational efficiency.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Gmail</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q-2BAF1F91</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Proven record in training, supervision, ward  management, and departmental __________ under high -pressure environments.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bahadur</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Environments</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q-FE7038E1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3,637,851/-, which is considerably higher than the calculated average __________ assessment.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Satellite</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q-F9ED460E</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>High-efficiency energy __________ and backup capability.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>While</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Aspect</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q-69D320B9</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>In view of the above __________ and financial analysis, installation of the proposed Hybrid Solar System with Lithium-Ion Battery Storage is recommended as a more sustainable, reliable, and economically beneficial solution.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q-F79E7902</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>However, the quoted price submitted by M/s Solar Square for the proposed __________ is Rs.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Appropriate</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q-9F8E0ACE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum __________ benefit to the organization.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kindly</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Q-42279AF8</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>26,000/- per month The approximate cost of a complete 6 kW __________ Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Q-CFBF996F</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Since the procurement involves multiple __________ systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rates</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Q-30E0D63D</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Maintenance requirements and operational losses are significantly __________.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Achieve</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Further</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Reflects</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Q-C4F2C3A3</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hence: Estimated Payback Period = 1,000,000 ÷ 26,000 Approximate Payback Period = 3.2 years After completion of the payback period, the generated electricity shall effectively become a long-term __________ saving for the organization/user.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Aspect</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Considerably</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Q-F88B3A8D</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>__________ batteries provide significantly longer service life compared to liquid batteries.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Attached</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Q-522C1BD1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Conventional liquid batteries generally provide only around 50% usable capacity of their rated __________.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Square</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Reflects</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Considered</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Q-22F017A6</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>50 per unit, therefore: __________ Monthly Savings = 520 × 50 Estimated Monthly Savings = Rs.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Since</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Q-5B7525FE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Benefits of Hybrid Solar System with Lithium-Ion Battery In view of the revised net metering policies, the __________ benefits of exporting excess power to the grid have reduced considerably.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Warranty</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Q-E03AEB02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>__________ depth of discharge and better energy utilization.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Approximately</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Negotiation</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Q-F3F62078</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Therefore, approval may kindly be accorded for further negotiation with the vendor so as to align the final awarded cost closer to the evaluated average market value and ensure maximum __________ benefit to the organization.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Exists</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Warranty</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Q-ACE088AE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Conventional liquid batteries generally provide only around 50% usable capacity of their rated __________.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Considered</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Technically</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Q-D78868E4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>High-efficiency energy __________ and backup capability.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>While</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Q-0264F0C4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Since the procurement involves multiple __________ systems with lithium-ion battery backup and hybrid inverter technology, there exists reasonable margin for price negotiation and optimization.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Q-F6D1DB1F</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>However, the quoted price submitted by M/s Solar Square for the proposed __________ is Rs.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Approximately</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Q-524ADD91</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>__________ depth of discharge and better energy utilization.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Detailed</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Q-6DB43A32</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>50 per unit, therefore: __________ Monthly Savings = 520 × 50 Estimated Monthly Savings = Rs.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Accorded</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Q-49C459BF</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Hence: Estimated Payback Period = 1,000,000 ÷ 26,000 Approximate Payback Period = 3.2 years After completion of the payback period, the generated electricity shall effectively become a long-term __________ saving for the organization/user.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Inverter</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Q-810981E7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>26,000/- per month The approximate cost of a complete 6 kW __________ Solar System with Lithium-Ion Battery and Hybrid Inverter is around Rs.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Q-B4FF7134</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>__________ batteries provide significantly longer service life compared to liquid batteries.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Installation</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Lithium-Ion</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
         </is>
       </c>
     </row>
@@ -2363,7 +6380,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -2451,7 +6468,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -2539,7 +6556,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -2627,7 +6644,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -2715,7 +6732,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -2803,7 +6820,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -2891,7 +6908,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -2979,7 +6996,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3067,7 +7084,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3155,7 +7172,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3243,7 +7260,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3331,7 +7348,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3419,7 +7436,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3507,7 +7524,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3595,7 +7612,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3683,7 +7700,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3745,8 +7762,11 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Not Attempted</t>
-        </is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>24.19</v>
       </c>
       <c r="N18" t="n">
         <v>80</v>
@@ -3766,12 +7786,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Recording viewed.</t>
+          <t>MCQ submitted. Correct 15/62</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3859,7 +7879,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2026-05-22 07:33:35</t>
+          <t>2026-05-22 14:37:29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +7894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3931,6 +7951,65 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>Generated_By</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NOTIF-30D0D023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>usama.saleem@psbureau.org</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Training Assigned: Demo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dear Usama Saleem,
+Training: Demo
+Schedule: 2026-05-22 10:00 AM
+Meeting: https://teams.microsoft.com/l/meeting/new?subject=Demo+-+TRN-27045916&amp;content=Training+ID%3A+TRN-27045916%0ATraining+Title%3A+Demo%0ASchedule%3A+2026-05-22+10%3A00+AM%0A%0APlease+join+this+HRDM+training+session+through+Microsoft+Teams.
+Slides: https://docs.google.com/presentation/d/18SCy_pTzsXZNqHYzPwNoUX53MBAvcyH7/edit?usp=sharing&amp;ouid=117387528328351609361&amp;rtpof=true&amp;sd=true
+Video: https://drive.google.com/file/d/1vJ7WPFIQGofvFa3bucnE4tr_SZKKSMXx/view?usp=sharing
+Regards,
+Human Resource Development and Management</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
         </is>
       </c>
     </row>
@@ -4016,7 +8095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7046,6 +11125,951 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>LOG-6B206A78</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:13:53</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LOG-11739387</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:41:49</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LOG-F2FBCA1D</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:43:27</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MCQs Generated</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>13 questions from 4 file(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>LOG-838AB62D</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:54:35</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>LOG-BD6E0E1B</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:58:54</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MCQs Generated</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>13 questions from 4 file(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LOG-F934E5B0</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:50:30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>LOG-DC54CF7C</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:51:04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MCQs Generated</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>10 questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>LOG-12440EFE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:59:10</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MCQs Generated</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2 questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>LOG-28DAEA3C</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:00:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MCQs Generated</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>14 questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LOG-A1A446A1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:33:17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>LOG-89429906</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:34:02</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Attendance Marked</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LOG-B083EDFC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:34:49</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Recording Saved</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LOG-18E7A96B</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:13</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Notifications Generated</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LOG-728A022A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:48</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MCQs Generated</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>10 questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LOG-AAC71159</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:35:56</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>User Logout</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Training Officer</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>USR-TRAINER</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>LOG-3ADABF30</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:36:21</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>User Login</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Successful login</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>LOG-B5B75673</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:36:59</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Recording Viewed</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>LOG-5835F75D</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:37:06</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Video Opened</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Video completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>LOG-FC251726</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:37:09</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Slides Opened</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Slides completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>LOG-1027E3AE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:37:28</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MCQ Test Submitted</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Usama Saleem</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Plan Appraiser</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>USR-9A35B777</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>TRN-27045916</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>24.19% Failed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
